--- a/Documentation/Best For Weighting Tables/Best for Anxiety.xlsx
+++ b/Documentation/Best For Weighting Tables/Best for Anxiety.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Tim Thomasson\Interactive-Pet-Marketplace\Documentation\Best For Weighting Tables\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F0B77A67-B3D2-4264-9F90-AE500C76A0EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F351C8A-18E6-461F-B770-90D09794F0F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{45A27E05-60E5-4906-BFBF-D5ADE38C7808}"/>
   </bookViews>
@@ -50,9 +50,6 @@
     <t>Emotional comfort potential</t>
   </si>
   <si>
-    <t>Noise sensitivity fit</t>
-  </si>
-  <si>
     <t>Safety risk</t>
   </si>
   <si>
@@ -66,13 +63,16 @@
   </si>
   <si>
     <t>Tactile comfort</t>
+  </si>
+  <si>
+    <t>Sound quality</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -92,10 +92,12 @@
       <b/>
       <sz val="11"/>
       <name val="Aptos Narrow"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
       <name val="Aptos Narrow"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -459,13 +461,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{96060508-9043-4148-A783-D31269D00DD7}">
   <dimension ref="A1:B8"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="29.28515625" customWidth="1"/>
     <col min="2" max="2" width="18.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" s="2" customFormat="1">
+    <row r="1" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -473,7 +475,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>2</v>
       </c>
@@ -481,49 +483,49 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="3" spans="1:2">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="B3" s="4">
         <v>0.15</v>
       </c>
     </row>
-    <row r="4" spans="1:2">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B4" s="4">
         <v>0.05</v>
       </c>
     </row>
-    <row r="5" spans="1:2">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B5" s="4">
         <v>0.1</v>
       </c>
     </row>
-    <row r="6" spans="1:2">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B6" s="4">
         <v>0.1</v>
       </c>
     </row>
-    <row r="7" spans="1:2">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B7" s="4">
         <v>0.1</v>
       </c>
     </row>
-    <row r="8" spans="1:2">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B8" s="4">
         <v>0.25</v>
